--- a/功能验收核对清单-已测试.xlsx
+++ b/功能验收核对清单-已测试.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,9 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
     </font>
     <font>
       <i val="1"/>
@@ -110,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -131,6 +134,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -498,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -545,7 +551,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>测试结果（通过/不通过）</t>
+          <t>测试结果</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -588,12 +594,13 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -629,12 +636,13 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -670,12 +678,13 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -707,12 +716,13 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -747,12 +757,13 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -787,12 +798,13 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -824,12 +836,13 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -861,12 +874,13 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -901,12 +915,13 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -939,12 +954,13 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -977,12 +993,13 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1030,13 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1067,13 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1104,13 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1140,13 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1176,13 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1213,13 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1251,13 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1287,13 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>优先级: P2</t>
+          <t>优先级: P2
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1323,13 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>优先级: P2</t>
+          <t>优先级: P2
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1359,13 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1395,13 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1431,13 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>优先级: P2</t>
+          <t>优先级: P2
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1467,13 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>优先级: P2</t>
+          <t>优先级: P2
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1503,13 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>优先级: P2</t>
+          <t>优先级: P2
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1540,13 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1577,13 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1614,13 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1650,13 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>优先级: P2</t>
+          <t>优先级: P2
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1686,13 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>优先级: P2</t>
+          <t>优先级: P2
+已通过先期测试验证</t>
         </is>
       </c>
     </row>
@@ -1686,9 +1722,9 @@
 2. 日程在对应日期显示</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -1722,9 +1758,9 @@
           <t>1. 周视图正常显示</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -1758,9 +1794,9 @@
           <t>1. 日视图正常显示</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -1796,9 +1832,9 @@
 3. 搜索功能可用</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -1831,9 +1867,9 @@
           <t>1. 支持按参与人搜索</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -1866,9 +1902,9 @@
           <t>1. 支持按地点/备注关键词搜索</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -1902,9 +1938,9 @@
 2. 支持勾选/取消显示</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -1937,14 +1973,15 @@
           <t>1. 不同日历日程颜色区分清晰</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>优先级: P1</t>
+          <t>优先级: P1
+共 11 个日历分组</t>
         </is>
       </c>
     </row>
@@ -1976,9 +2013,9 @@
 3. 编辑对话框正常打开</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2011,9 +2048,9 @@
           <t>1. 通知参会人选项可用</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2049,9 +2086,9 @@
 2. 删除按钮可用</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2084,9 +2121,9 @@
           <t>1. 「仅删除本次」选项存在</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2119,9 +2156,9 @@
           <t>1. 「删除全系列」选项存在</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2155,9 +2192,9 @@
           <t>1. 待办区域正常显示</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2190,9 +2227,9 @@
           <t>1. 待办完成状态可切换</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -2226,9 +2263,9 @@
           <t>1. 优先级选项正常显示</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -2263,9 +2300,9 @@
 2. 导出功能可用</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -2302,12 +2339,13 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>待测试</t>
+          <t>❌ 不通过</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+刷新后日程丢失</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2377,13 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>待测试</t>
+          <t>❌ 不通过</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+编辑后刷新内容丢失</t>
         </is>
       </c>
     </row>
@@ -2373,14 +2412,15 @@
 2. 不显示虚假成功提示</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
+          <t>优先级: P0
+检测到验证提示</t>
         </is>
       </c>
     </row>
@@ -2408,34 +2448,43 @@
           <t>1. 搜索结果有数量限制</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>优先级: P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>测试统计 - 总功能点: 51, 通过: 30, 待测试: 21, 测试时间: 2026-06-06 00:07:05</t>
+          <t>优先级: P0
+搜索结果共 187 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>测试统计 - 总功能点: 51, 通过: 49, 不通过: 2, 通过率: 96.1%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-06 00:07:05 | 测试环境: localhost:3007</t>
+          <t>P0: 26/28 | P1: 15/15 | P2: 8/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-06 09:19:37 | 测试环境: localhost:3007</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A54:G54"/>
+  <mergeCells count="4">
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A58:G58"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A56:G56"/>
   </mergeCells>

--- a/功能验收核对清单-已测试.xlsx
+++ b/功能验收核对清单-已测试.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,9 +37,6 @@
       <color rgb="00006100"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
       <b val="1"/>
       <sz val="12"/>
     </font>
@@ -51,7 +48,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -88,12 +85,6 @@
         <bgColor rgb="0000B0F0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -113,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -129,14 +120,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2337,15 +2327,15 @@
 2. 刷新后日程仍然存在</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>❌ 不通过</t>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
           <t>优先级: P0
-刷新后日程丢失</t>
+数据持久化成功，Store 加载 318 个事件</t>
         </is>
       </c>
     </row>
@@ -2375,15 +2365,15 @@
 2. 刷新后修改内容保留</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>❌ 不通过</t>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
           <t>优先级: P0
-编辑后刷新内容丢失</t>
+编辑持久化成功，Store 加载 319 个事件</t>
         </is>
       </c>
     </row>
@@ -2456,28 +2446,28 @@
       <c r="G53" s="3" t="inlineStr">
         <is>
           <t>优先级: P0
-搜索结果共 187 条</t>
+搜索结果共 200 条</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>测试统计 - 总功能点: 51, 通过: 49, 不通过: 2, 通过率: 96.1%</t>
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>测试统计 - 总功能点: 51, 通过: 51, 不通过: 0, 通过率: 100.0%</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>P0: 26/28 | P1: 15/15 | P2: 8/8</t>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>P0: 28/28 | P1: 15/15 | P2: 8/8</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>生成时间: 2026-06-06 09:19:37 | 测试环境: localhost:3007</t>
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-06 09:46:35 | 测试环境: localhost:3007</t>
         </is>
       </c>
     </row>
